--- a/10_Threshold_OUTPUT/reverse_Q3K4G1_Pseudomonas_fluorescens_Pf0-1.xlsx
+++ b/10_Threshold_OUTPUT/reverse_Q3K4G1_Pseudomonas_fluorescens_Pf0-1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TGTCACA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TGT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>ACA</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;C&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.827469012395042</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>TGTCACACA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TGT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>ACA</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;CAC&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.983406637345062</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>CTGTCA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;GT&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -564,15 +604,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>TGTCA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;T&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.3016793282686925</v>
       </c>
     </row>
@@ -593,15 +643,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>TGTCACAC</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;TCAC&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -622,15 +682,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>ACAC</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -651,15 +721,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>TGTCACACAA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;TCACAC&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -680,15 +760,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>CACACAAC</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;CACA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -709,15 +799,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>CACACAACTG</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;CACAAC&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.9692123150739704</v>
       </c>
     </row>
@@ -738,15 +838,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>ACACAACTGT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;ACAACT&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.9940023990403839</v>
       </c>
     </row>
@@ -767,15 +877,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>ACAACTGT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;AACT&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>0.9996001599360256</v>
       </c>
     </row>
@@ -796,15 +916,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>TGTCACACAACTGTCA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;TCACACAACTGT&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>0.2375049980007997</v>
       </c>
     </row>
@@ -825,15 +955,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>CACAACTGTCA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;CAACTGT&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -854,15 +994,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>ACTGTCA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;TGT&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -883,15 +1033,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>TGTCA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;T&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>0.950219912035186</v>
       </c>
     </row>

--- a/10_Threshold_OUTPUT/reverse_Q3K4G1_Pseudomonas_fluorescens_Pf0-1.xlsx
+++ b/10_Threshold_OUTPUT/reverse_Q3K4G1_Pseudomonas_fluorescens_Pf0-1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>p_value</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -508,6 +513,11 @@
       <c r="I2" t="n">
         <v>0.827469012395042</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -547,6 +557,11 @@
       <c r="I3" t="n">
         <v>0.983406637345062</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -585,6 +600,11 @@
       </c>
       <c r="I4" t="n">
         <v>0.9998000799680128</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -625,6 +645,11 @@
       <c r="I5" t="n">
         <v>0.3016793282686925</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -664,6 +689,11 @@
       <c r="I6" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -703,6 +733,11 @@
       <c r="I7" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -742,6 +777,11 @@
       <c r="I8" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -781,6 +821,11 @@
       <c r="I9" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -820,6 +865,11 @@
       <c r="I10" t="n">
         <v>0.9692123150739704</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -859,6 +909,11 @@
       <c r="I11" t="n">
         <v>0.9940023990403839</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -898,6 +953,11 @@
       <c r="I12" t="n">
         <v>0.9996001599360256</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -937,6 +997,11 @@
       <c r="I13" t="n">
         <v>0.2375049980007997</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -976,6 +1041,11 @@
       <c r="I14" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1015,6 +1085,11 @@
       <c r="I15" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1053,6 +1128,11 @@
       </c>
       <c r="I16" t="n">
         <v>0.950219912035186</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/10_Threshold_OUTPUT/reverse_Q3K4G1_Pseudomonas_fluorescens_Pf0-1.xlsx
+++ b/10_Threshold_OUTPUT/reverse_Q3K4G1_Pseudomonas_fluorescens_Pf0-1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>evaluation</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>correctness_%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -518,6 +523,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -562,6 +570,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -605,6 +616,9 @@
         <is>
           <t>Ambiguous IR</t>
         </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -650,6 +664,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -694,6 +711,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -738,6 +758,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -782,6 +805,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -826,6 +852,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -870,6 +899,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -914,6 +946,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -958,6 +993,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1002,6 +1040,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1046,6 +1087,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1090,6 +1134,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1133,6 +1180,9 @@
         <is>
           <t>Confirmed IR</t>
         </is>
+      </c>
+      <c r="K16" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
